--- a/data/trans_dic/P79$recibos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79$recibos_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 13,64</t>
+          <t>5,62; 15,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 22,53</t>
+          <t>10,46; 21,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 15,66</t>
+          <t>9,06; 16,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,41</t>
+          <t>4,67; 10,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,75</t>
+          <t>6,95; 12,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,28</t>
+          <t>6,47; 10,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 8,3</t>
+          <t>4,68; 9,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,72</t>
+          <t>5,98; 9,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,79</t>
+          <t>5,8; 8,55</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,84</t>
+          <t>6,37; 10,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 9,36</t>
+          <t>6,9; 10,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,26</t>
+          <t>7,21; 9,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 12,15</t>
+          <t>8,07; 12,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,53</t>
+          <t>9,48; 13,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,01</t>
+          <t>9,27; 12,62</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,09; 11,92</t>
+          <t>7,38; 12,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 10,11</t>
+          <t>7,68; 12,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,12</t>
+          <t>8,08; 11,35</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 12,54</t>
+          <t>7,15; 12,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 10,94</t>
+          <t>7,42; 11,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,89</t>
+          <t>8,05; 11,33</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,6</t>
+          <t>7,65; 9,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 9,77</t>
+          <t>8,95; 10,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,98</t>
+          <t>8,54; 9,94</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28602</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>50768</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>87240</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16403; 50513</t>
+          <t>21227; 58604</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31175; 65189</t>
+          <t>35296; 71104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53725; 103308</t>
+          <t>64831; 118550</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>28044</t>
+          <t>34078</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>44870</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68087</t>
+          <t>78948</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17569; 43302</t>
+          <t>21913; 49443</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28847; 54844</t>
+          <t>33659; 60397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52175; 86992</t>
+          <t>61715; 101825</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31282</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>46255</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70071</t>
+          <t>85265</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21271; 43443</t>
+          <t>28058; 54722</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27029; 50362</t>
+          <t>36172; 58893</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54630; 85719</t>
+          <t>69920; 103055</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>56419</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>117934</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19934; 77177</t>
+          <t>43454; 74473</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41480; 65040</t>
+          <t>49464; 73625</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60026; 129485</t>
+          <t>100848; 138338</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53370</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>67481</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111849</t>
+          <t>128078</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>42103; 66147</t>
+          <t>47691; 75005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>48420; 71142</t>
+          <t>55583; 80300</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94577; 128583</t>
+          <t>109141; 148566</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>34183</t>
+          <t>37820</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70877</t>
+          <t>79235</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25520; 42891</t>
+          <t>29279; 47822</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14613; 60369</t>
+          <t>32726; 51623</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32453; 96871</t>
+          <t>66502; 93405</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26350</t>
+          <t>29294</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>36140</t>
+          <t>41449</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>62490</t>
+          <t>70743</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19844; 34756</t>
+          <t>21750; 38211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28214; 44432</t>
+          <t>32842; 51369</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51293; 74454</t>
+          <t>60093; 84553</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>250281</t>
+          <t>293689</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>309045</t>
+          <t>353753</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>559326</t>
+          <t>647442</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>195743; 289261</t>
+          <t>261531; 331263</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>252569; 344051</t>
+          <t>322238; 385949</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>481189; 618283</t>
+          <t>599265; 697938</t>
         </is>
       </c>
     </row>
